--- a/results/04_final_refined_daily_hydroclimate_data/702/Min_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Min_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -442,7 +442,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>10.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -470,7 +470,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -483,8 +483,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>10.7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -497,8 +497,8 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
-        <v>4</v>
+      <c r="D8">
+        <v>10.9</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -525,8 +525,8 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
-        <v>4</v>
+      <c r="D10">
+        <v>13.1</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>11</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15">
-        <v>12.6</v>
+      <c r="D15" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16">
-        <v>12.2</v>
+      <c r="D16" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="D17">
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -652,7 +652,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>17.1</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -680,7 +680,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -750,7 +750,7 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>10.54</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -764,7 +764,7 @@
         <v>26</v>
       </c>
       <c r="D27">
-        <v>10.9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -791,8 +791,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29">
-        <v>8.6</v>
+      <c r="D29" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -805,8 +805,8 @@
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30">
-        <v>11.4</v>
+      <c r="D30" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -834,7 +834,7 @@
         <v>2</v>
       </c>
       <c r="D32">
-        <v>15.1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -848,7 +848,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -889,8 +889,8 @@
       <c r="C36">
         <v>6</v>
       </c>
-      <c r="D36" t="s">
-        <v>4</v>
+      <c r="D36">
+        <v>16.1</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -917,8 +917,8 @@
       <c r="C38">
         <v>8</v>
       </c>
-      <c r="D38" t="s">
-        <v>4</v>
+      <c r="D38">
+        <v>11.6</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
       <c r="D39">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -973,8 +973,8 @@
       <c r="C42">
         <v>12</v>
       </c>
-      <c r="D42" t="s">
-        <v>4</v>
+      <c r="D42">
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -987,8 +987,8 @@
       <c r="C43">
         <v>13</v>
       </c>
-      <c r="D43" t="s">
-        <v>4</v>
+      <c r="D43">
+        <v>12.54</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1015,8 +1015,8 @@
       <c r="C45">
         <v>15</v>
       </c>
-      <c r="D45" t="s">
-        <v>4</v>
+      <c r="D45">
+        <v>13.2</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1029,8 +1029,8 @@
       <c r="C46">
         <v>16</v>
       </c>
-      <c r="D46" t="s">
-        <v>4</v>
+      <c r="D46">
+        <v>15.5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1044,7 +1044,7 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1085,8 +1085,8 @@
       <c r="C50">
         <v>20</v>
       </c>
-      <c r="D50" t="s">
-        <v>4</v>
+      <c r="D50">
+        <v>13.3</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1142,7 +1142,7 @@
         <v>24</v>
       </c>
       <c r="D54">
-        <v>12</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1184,7 +1184,7 @@
         <v>27</v>
       </c>
       <c r="D57">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1198,7 +1198,7 @@
         <v>28</v>
       </c>
       <c r="D58">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1211,8 +1211,8 @@
       <c r="C59">
         <v>29</v>
       </c>
-      <c r="D59">
-        <v>10.4</v>
+      <c r="D59" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1225,8 +1225,8 @@
       <c r="C60">
         <v>30</v>
       </c>
-      <c r="D60" t="s">
-        <v>4</v>
+      <c r="D60">
+        <v>12.5</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/702/Min_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Min_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Min_Temperature</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -442,7 +439,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>7.9</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -470,7 +467,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -512,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -526,7 +523,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>13.1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -540,7 +537,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>10.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -595,8 +592,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>4</v>
+      <c r="D15">
+        <v>12.7</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -609,8 +606,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
-        <v>4</v>
+      <c r="D16">
+        <v>12.1</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -652,7 +649,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -750,7 +747,7 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -791,8 +788,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>4</v>
+      <c r="D29">
+        <v>8.6</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -805,8 +802,8 @@
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30" t="s">
-        <v>4</v>
+      <c r="D30">
+        <v>11.4</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -890,7 +887,7 @@
         <v>6</v>
       </c>
       <c r="D36">
-        <v>16.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -988,7 +985,7 @@
         <v>13</v>
       </c>
       <c r="D43">
-        <v>12.54</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1002,7 +999,7 @@
         <v>14</v>
       </c>
       <c r="D44">
-        <v>14.1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1016,7 +1013,7 @@
         <v>15</v>
       </c>
       <c r="D45">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1086,7 +1083,7 @@
         <v>20</v>
       </c>
       <c r="D50">
-        <v>13.3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1099,8 +1096,8 @@
       <c r="C51">
         <v>21</v>
       </c>
-      <c r="D51" t="s">
-        <v>4</v>
+      <c r="D51">
+        <v>11.4</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1127,8 +1124,8 @@
       <c r="C53">
         <v>23</v>
       </c>
-      <c r="D53" t="s">
-        <v>4</v>
+      <c r="D53">
+        <v>13.1</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1142,7 +1139,7 @@
         <v>24</v>
       </c>
       <c r="D54">
-        <v>12.1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1184,7 +1181,7 @@
         <v>27</v>
       </c>
       <c r="D57">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1211,8 +1208,8 @@
       <c r="C59">
         <v>29</v>
       </c>
-      <c r="D59" t="s">
-        <v>4</v>
+      <c r="D59">
+        <v>10.4</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1226,7 +1223,7 @@
         <v>30</v>
       </c>
       <c r="D60">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/702/Min_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Min_Temperature_timeseries.xlsx
@@ -607,7 +607,7 @@
         <v>15</v>
       </c>
       <c r="D16">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -663,7 +663,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -887,7 +887,7 @@
         <v>6</v>
       </c>
       <c r="D36">
-        <v>7.2</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1125,7 +1125,7 @@
         <v>23</v>
       </c>
       <c r="D53">
-        <v>13.1</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1209,7 +1209,7 @@
         <v>29</v>
       </c>
       <c r="D59">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="60" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/702/Min_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/702/Min_Temperature_timeseries.xlsx
@@ -1125,7 +1125,7 @@
         <v>23</v>
       </c>
       <c r="D53">
-        <v>15.1</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="54" spans="1:4">
